--- a/changes/fal-stocks.xlsx
+++ b/changes/fal-stocks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-balancing\changes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yifan/Documents/deadline-balancing/changes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B681E1-7D42-473B-BD6C-8C519D2AB0F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A49F44-6F3B-6243-9E64-B49F112E7D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="m4-barrels" sheetId="1" r:id="rId1"/>
@@ -1032,19 +1032,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N41"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.85546875" customWidth="1"/>
-    <col min="2" max="2" width="42.140625" customWidth="1"/>
-    <col min="3" max="22" width="6.7109375" customWidth="1"/>
+    <col min="1" max="1" width="32.83203125" customWidth="1"/>
+    <col min="2" max="2" width="35.5" customWidth="1"/>
+    <col min="3" max="22" width="6.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>-1.2</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>10</v>
       </c>
       <c r="D4">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="E4">
         <v>-10</v>
@@ -1139,10 +1139,10 @@
       </c>
       <c r="N4">
         <f t="shared" ref="N4:N40" si="0">C4-D4*20-E4*0.8-F4*0.6-H4*5+I4*10+J4/300</f>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -1156,20 +1156,20 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="E5">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="F5">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="M5">
         <v>500</v>
       </c>
       <c r="N5">
         <f t="shared" si="0"/>
-        <v>17.799999999999997</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+        <v>17.400000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -1207,17 +1207,17 @@
         <v>-11</v>
       </c>
       <c r="F7">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="M7">
         <v>1200</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
-        <v>17.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>39</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>0.05</v>
@@ -1265,10 +1265,10 @@
       </c>
       <c r="N9">
         <f t="shared" si="0"/>
-        <v>-10.7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+        <v>-9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1276,10 +1276,10 @@
         <v>18</v>
       </c>
       <c r="C10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="E10">
         <v>-7</v>
@@ -1291,11 +1291,11 @@
         <v>500</v>
       </c>
       <c r="N10">
-        <f t="shared" si="0"/>
-        <v>19.200000000000003</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+        <f>C10-D10*20-E10*0.8-F10*0.6-H10*5+I10*10+J10/300</f>
+        <v>18.799999999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>0.05</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11">
         <v>2</v>
@@ -1321,11 +1321,11 @@
         <v>1000</v>
       </c>
       <c r="N11">
-        <f t="shared" si="0"/>
-        <v>-7.05</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+        <f>C11-D11*20-E11*0.8-F11*0.6-H11*5+I11*10+J11/300</f>
+        <v>-6.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1336,10 +1336,10 @@
         <v>13</v>
       </c>
       <c r="D12">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="E12">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="F12">
         <v>-7</v>
@@ -1351,11 +1351,11 @@
         <v>3000</v>
       </c>
       <c r="N12">
-        <f t="shared" si="0"/>
-        <v>20.849999999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+        <f>C12-D12*20-E12*0.8-F12*0.6-H12*5+I12*10+J12/300</f>
+        <v>20.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -1363,17 +1363,17 @@
         <v>24</v>
       </c>
       <c r="D13">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="M13">
         <v>0</v>
       </c>
       <c r="N13">
-        <f t="shared" si="0"/>
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+        <f>C13-D13*20-E13*0.8-F13*0.6-H13*5+I13*10+J13/300</f>
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1387,11 +1387,11 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <f t="shared" si="0"/>
+        <f>C14-D14*20-E14*0.8-F14*0.6-H14*5+I14*10+J14/300</f>
         <v>-0.6</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -1402,17 +1402,17 @@
         <v>1</v>
       </c>
       <c r="D15">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
       <c r="N15">
-        <f t="shared" si="0"/>
-        <v>0.19999999999999996</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+        <f>C15-D15*20-E15*0.8-F15*0.6-H15*5+I15*10+J15/300</f>
+        <v>-0.19999999999999996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1429,11 +1429,11 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <f t="shared" si="0"/>
+        <f>C16-D16*20-E16*0.8-F16*0.6-H16*5+I16*10+J16/300</f>
         <v>0.19999999999999996</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
         <v>15</v>
@@ -1472,17 +1472,17 @@
         <v>1400</v>
       </c>
       <c r="N17">
-        <f t="shared" si="0"/>
+        <f>C17-D17*20-E17*0.8-F17*0.6-H17*5+I17*10+J17/300</f>
         <v>24.8</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="N18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+        <f>C18-D18*20-E18*0.8-F18*0.6-H18*5+I18*10+J18/300</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>40</v>
       </c>
@@ -1491,51 +1491,51 @@
         <v>10</v>
       </c>
       <c r="D19">
-        <f t="shared" ref="D19:M19" si="1">D4</f>
-        <v>0.35</v>
+        <f>D4</f>
+        <v>0.36</v>
       </c>
       <c r="E19">
-        <f t="shared" si="1"/>
+        <f>E4</f>
         <v>-10</v>
       </c>
       <c r="F19">
-        <f t="shared" si="1"/>
+        <f>F4</f>
         <v>-10</v>
       </c>
       <c r="G19">
-        <f t="shared" si="1"/>
+        <f>G4</f>
         <v>0</v>
       </c>
       <c r="H19">
-        <f t="shared" si="1"/>
+        <f>H4</f>
         <v>0</v>
       </c>
       <c r="I19">
-        <f t="shared" si="1"/>
+        <f>I4</f>
         <v>0</v>
       </c>
       <c r="J19">
-        <f t="shared" si="1"/>
+        <f>J4</f>
         <v>0</v>
       </c>
       <c r="K19">
-        <f t="shared" si="1"/>
+        <f>K4</f>
         <v>0</v>
       </c>
       <c r="L19">
-        <f t="shared" si="1"/>
+        <f>L4</f>
         <v>0</v>
       </c>
       <c r="M19">
-        <f t="shared" si="1"/>
+        <f>M4</f>
         <v>0</v>
       </c>
       <c r="N19">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>41</v>
       </c>
@@ -1544,51 +1544,51 @@
         <v>10</v>
       </c>
       <c r="D20">
-        <f t="shared" ref="D20:M20" si="2">D8+D7</f>
+        <f>D8+D7</f>
         <v>0.42000000000000004</v>
       </c>
       <c r="E20">
-        <f t="shared" si="2"/>
+        <f>E8+E7</f>
         <v>-11</v>
       </c>
       <c r="F20">
-        <f t="shared" si="2"/>
-        <v>-12</v>
+        <f>F8+F7</f>
+        <v>-11</v>
       </c>
       <c r="G20">
-        <f t="shared" si="2"/>
+        <f>G8+G7</f>
         <v>0</v>
       </c>
       <c r="H20">
-        <f t="shared" si="2"/>
+        <f>H8+H7</f>
         <v>0</v>
       </c>
       <c r="I20">
-        <f t="shared" si="2"/>
+        <f>I8+I7</f>
         <v>0</v>
       </c>
       <c r="J20">
-        <f t="shared" si="2"/>
+        <f>J8+J7</f>
         <v>0</v>
       </c>
       <c r="K20">
-        <f t="shared" si="2"/>
+        <f>K8+K7</f>
         <v>0</v>
       </c>
       <c r="L20">
-        <f t="shared" si="2"/>
+        <f>L8+L7</f>
         <v>0</v>
       </c>
       <c r="M20">
-        <f t="shared" si="2"/>
+        <f>M8+M7</f>
         <v>1200</v>
       </c>
       <c r="N20">
         <f t="shared" si="0"/>
-        <v>17.600000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
         <v>46</v>
@@ -1598,159 +1598,159 @@
         <v>13</v>
       </c>
       <c r="D21" s="1">
-        <f t="shared" ref="D21:M21" si="3">D5+D6</f>
+        <f>D5+D6</f>
         <v>0.33999999999999997</v>
       </c>
       <c r="E21" s="1">
-        <f t="shared" si="3"/>
-        <v>-10</v>
+        <f>E5+E6</f>
+        <v>-8</v>
       </c>
       <c r="F21" s="1">
-        <f t="shared" si="3"/>
-        <v>-6</v>
+        <f>F5+F6</f>
+        <v>-8</v>
       </c>
       <c r="G21" s="1">
-        <f t="shared" si="3"/>
+        <f>G5+G6</f>
         <v>0</v>
       </c>
       <c r="H21" s="1">
-        <f t="shared" si="3"/>
+        <f>H5+H6</f>
         <v>0</v>
       </c>
       <c r="I21" s="1">
-        <f t="shared" si="3"/>
+        <f>I5+I6</f>
         <v>0</v>
       </c>
       <c r="J21" s="1">
-        <f t="shared" si="3"/>
+        <f>J5+J6</f>
         <v>0</v>
       </c>
       <c r="K21" s="1">
-        <f t="shared" si="3"/>
+        <f>K5+K6</f>
         <v>0</v>
       </c>
       <c r="L21" s="1">
-        <f t="shared" si="3"/>
+        <f>L5+L6</f>
         <v>0</v>
       </c>
       <c r="M21" s="1">
-        <f t="shared" si="3"/>
+        <f>M5+M6</f>
         <v>500</v>
       </c>
       <c r="N21">
         <f t="shared" si="0"/>
-        <v>17.8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+        <v>17.400000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C22" s="1">
         <f>C9</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" s="1">
-        <f t="shared" ref="D22:M22" si="4">D9</f>
+        <f>D9</f>
         <v>0.05</v>
       </c>
       <c r="E22" s="1">
-        <f t="shared" si="4"/>
+        <f>E9</f>
         <v>8</v>
       </c>
       <c r="F22" s="1">
-        <f t="shared" si="4"/>
+        <f>F9</f>
         <v>8</v>
       </c>
       <c r="G22" s="1">
-        <f t="shared" si="4"/>
+        <f>G9</f>
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <f t="shared" si="4"/>
+        <f>H9</f>
         <v>0.5</v>
       </c>
       <c r="I22" s="1">
-        <f t="shared" si="4"/>
+        <f>I9</f>
         <v>0</v>
       </c>
       <c r="J22" s="1">
-        <f t="shared" si="4"/>
+        <f>J9</f>
         <v>0</v>
       </c>
       <c r="K22" s="1">
-        <f t="shared" si="4"/>
+        <f>K9</f>
         <v>0</v>
       </c>
       <c r="L22" s="1">
-        <f t="shared" si="4"/>
+        <f>L9</f>
         <v>0</v>
       </c>
       <c r="M22" s="1">
-        <f t="shared" si="4"/>
+        <f>M9</f>
         <v>1000</v>
       </c>
       <c r="N22">
         <f t="shared" si="0"/>
-        <v>-10.7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+        <v>-9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C23" s="1">
         <f>C10+C3</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D23" s="1">
-        <f t="shared" ref="D23:M23" si="5">D10+D3</f>
-        <v>0.31</v>
+        <f>D10+D3</f>
+        <v>0.38</v>
       </c>
       <c r="E23" s="1">
-        <f t="shared" si="5"/>
+        <f>E10+E3</f>
         <v>-7</v>
       </c>
       <c r="F23" s="1">
-        <f t="shared" si="5"/>
+        <f>F10+F3</f>
         <v>-11</v>
       </c>
       <c r="G23" s="1">
-        <f t="shared" si="5"/>
+        <f>G10+G3</f>
         <v>0</v>
       </c>
       <c r="H23" s="1">
-        <f t="shared" si="5"/>
+        <f>H10+H3</f>
         <v>0</v>
       </c>
       <c r="I23" s="1">
-        <f t="shared" si="5"/>
+        <f>I10+I3</f>
         <v>0</v>
       </c>
       <c r="J23" s="1">
-        <f t="shared" si="5"/>
+        <f>J10+J3</f>
         <v>0</v>
       </c>
       <c r="K23" s="1">
-        <f t="shared" si="5"/>
+        <f>K10+K3</f>
         <v>0</v>
       </c>
       <c r="L23" s="1">
-        <f t="shared" si="5"/>
+        <f>L10+L3</f>
         <v>0</v>
       </c>
       <c r="M23" s="1">
-        <f t="shared" si="5"/>
+        <f>M10+M3</f>
         <v>1000</v>
       </c>
       <c r="N23">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+        <v>17.600000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
         <v>49</v>
@@ -1760,51 +1760,51 @@
         <v>15</v>
       </c>
       <c r="D24" s="1">
-        <f t="shared" ref="D24:M24" si="6">D3+D12+D13+D14+D15+D16</f>
-        <v>0.39</v>
+        <f>D3+D12+D13+D14+D15+D16</f>
+        <v>0.49</v>
       </c>
       <c r="E24" s="1">
-        <f t="shared" si="6"/>
-        <v>-9</v>
+        <f>E3+E12+E13+E14+E15+E16</f>
+        <v>-10</v>
       </c>
       <c r="F24" s="1">
-        <f t="shared" si="6"/>
+        <f>F3+F12+F13+F14+F15+F16</f>
         <v>-7</v>
       </c>
       <c r="G24" s="1">
-        <f t="shared" si="6"/>
+        <f>G3+G12+G13+G14+G15+G16</f>
         <v>0</v>
       </c>
       <c r="H24" s="1">
-        <f t="shared" si="6"/>
+        <f>H3+H12+H13+H14+H15+H16</f>
         <v>-0.05</v>
       </c>
       <c r="I24" s="1">
-        <f t="shared" si="6"/>
+        <f>I3+I12+I13+I14+I15+I16</f>
         <v>0</v>
       </c>
       <c r="J24" s="1">
-        <f t="shared" si="6"/>
+        <f>J3+J12+J13+J14+J15+J16</f>
         <v>0</v>
       </c>
       <c r="K24" s="1">
-        <f t="shared" si="6"/>
+        <f>K3+K12+K13+K14+K15+K16</f>
         <v>0</v>
       </c>
       <c r="L24" s="1">
-        <f t="shared" si="6"/>
+        <f>L3+L12+L13+L14+L15+L16</f>
         <v>0</v>
       </c>
       <c r="M24" s="1">
-        <f t="shared" si="6"/>
+        <f>M3+M12+M13+M14+M15+M16</f>
         <v>3500</v>
       </c>
       <c r="N24">
         <f t="shared" si="0"/>
-        <v>18.849999999999998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+        <v>17.649999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
         <v>16</v>
@@ -1814,51 +1814,51 @@
         <v>14</v>
       </c>
       <c r="D25" s="1">
-        <f t="shared" ref="D25:M25" si="7">D3+D11+D17</f>
+        <f>D3+D11+D17</f>
         <v>0.45999999999999996</v>
       </c>
       <c r="E25" s="1">
-        <f t="shared" si="7"/>
-        <v>-9</v>
+        <f>E3+E11+E17</f>
+        <v>-10</v>
       </c>
       <c r="F25" s="1">
-        <f t="shared" si="7"/>
+        <f>F3+F11+F17</f>
         <v>-8</v>
       </c>
       <c r="G25" s="1">
-        <f t="shared" si="7"/>
+        <f>G3+G11+G17</f>
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <f t="shared" si="7"/>
+        <f>H3+H11+H17</f>
         <v>0.05</v>
       </c>
       <c r="I25" s="1">
-        <f t="shared" si="7"/>
+        <f>I3+I11+I17</f>
         <v>0</v>
       </c>
       <c r="J25" s="1">
-        <f t="shared" si="7"/>
+        <f>J3+J11+J17</f>
         <v>0</v>
       </c>
       <c r="K25" s="1">
-        <f t="shared" si="7"/>
+        <f>K3+K11+K17</f>
         <v>0</v>
       </c>
       <c r="L25" s="1">
-        <f t="shared" si="7"/>
+        <f>L3+L11+L17</f>
         <v>0</v>
       </c>
       <c r="M25" s="1">
-        <f t="shared" si="7"/>
+        <f>M3+M11+M17</f>
         <v>2900</v>
       </c>
       <c r="N25">
         <f t="shared" si="0"/>
-        <v>16.55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+        <v>17.350000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1896,7 +1896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1915,7 +1915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1953,7 +1953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1972,7 +1972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1991,7 +1991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2010,7 +2010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2029,7 +2029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2048,7 +2048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2067,7 +2067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2086,7 +2086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2105,7 +2105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2143,7 +2143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>

--- a/changes/fal-stocks.xlsx
+++ b/changes/fal-stocks.xlsx
@@ -497,6 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <dimension ref="A1:N41"/>
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
@@ -952,16 +953,24 @@
       <c r="B18" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0.08</v>
+      <c r="C18" t="inlineStr" s="4">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr" s="4">
+        <is>
+          <t>0.05</t>
+        </is>
       </c>
       <c r="E18" s="4">
         <v>-1.0</v>
       </c>
-      <c r="F18" s="4"/>
+      <c r="F18" t="inlineStr" s="4">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
@@ -1015,8 +1024,10 @@
       <c r="B20" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="4">
-        <v>8.0</v>
+      <c r="C20" t="inlineStr" s="4">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D20" s="4">
         <v>0.23</v>
@@ -1024,8 +1035,10 @@
       <c r="E20" s="4">
         <v>-10.0</v>
       </c>
-      <c r="F20" s="4">
-        <v>-10.0</v>
+      <c r="F20" t="inlineStr" s="4">
+        <is>
+          <t>-8</t>
+        </is>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
@@ -1046,8 +1059,10 @@
       <c r="B21" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="4">
-        <v>5.0</v>
+      <c r="C21" t="inlineStr" s="4">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="D21" s="4">
         <v>0.12</v>
